--- a/UsernameLogin.xlsx
+++ b/UsernameLogin.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AP_EXPRESS\Desktop\E-work-v12\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programing\Thefirst-E-work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E61C27E-795D-4070-9616-32BCBF54727C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937DF4AC-CB38-4FEC-B3E4-A581FE1C143E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="345" windowWidth="21600" windowHeight="11295" xr2:uid="{B44B7925-B293-4A2E-9224-D3AA907C5721}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B44B7925-B293-4A2E-9224-D3AA907C5721}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,30 +36,30 @@
     <t>Type</t>
   </si>
   <si>
+    <t>ระบบ</t>
+  </si>
+  <si>
     <t>ผู้กระทำการแทน</t>
   </si>
   <si>
-    <t>ระบบ</t>
-  </si>
-  <si>
-    <t>Modmod@mailforeign.com</t>
-  </si>
-  <si>
-    <t>Mod123456</t>
-  </si>
-  <si>
-    <t>e-Workpermit</t>
+    <t>E-Workpermit</t>
+  </si>
+  <si>
+    <t>Kanyaphat0</t>
+  </si>
+  <si>
+    <t>1509900662001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -68,7 +68,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="222"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -98,11 +105,11 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -118,7 +125,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ธีมของ Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -415,15 +422,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C5AE76-63C1-41C0-A454-E6BAD1112758}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="16.625" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -434,29 +441,30 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{221FB429-7439-4620-B1EC-CBCB31774BE7}"/>
+    <hyperlink ref="A2" r:id="rId1" display="Raweewan68297@mailforeign.com" xr:uid="{221FB429-7439-4620-B1EC-CBCB31774BE7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/UsernameLogin.xlsx
+++ b/UsernameLogin.xlsx
@@ -1,89 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programing\Thefirst-E-work\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937DF4AC-CB38-4FEC-B3E4-A581FE1C143E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B44B7925-B293-4A2E-9224-D3AA907C5721}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>ระบบ</t>
-  </si>
-  <si>
-    <t>ผู้กระทำการแทน</t>
-  </si>
-  <si>
-    <t>E-Workpermit</t>
-  </si>
-  <si>
-    <t>Kanyaphat0</t>
-  </si>
-  <si>
-    <t>1509900662001</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="Tahoma"/>
+      <charset val="222"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="222"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <name val="Tahoma"/>
+      <charset val="222"/>
+      <family val="2"/>
+      <color theme="10"/>
       <sz val="11"/>
-      <color theme="10"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="222"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Tahoma"/>
+      <charset val="222"/>
+      <family val="2"/>
       <sz val="8"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="222"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -100,27 +61,86 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -420,51 +440,70 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C5AE76-63C1-41C0-A454-E6BAD1112758}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="16.625" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="13.875" customWidth="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="16.625" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13.875" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Username</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Password</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ระบบ</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>woraphitcha.opall@gmail.com</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Opwrpch13</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ผู้กระทำการแทน</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>E-Workpermit</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="Raweewan68297@mailforeign.com" xr:uid="{221FB429-7439-4620-B1EC-CBCB31774BE7}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" display="Raweewan68297@mailforeign.com" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/UsernameLogin.xlsx
+++ b/UsernameLogin.xlsx
@@ -1,50 +1,90 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\Desktop\E-work\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB1F36F-8A67-4C8A-90AD-CA9EBBAA1DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="3510" yWindow="1110" windowWidth="21390" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>ระบบ</t>
+  </si>
+  <si>
+    <t>E-Workpermit</t>
+  </si>
+  <si>
+    <t>บริษัทนำเข้า (บนจ.)</t>
+  </si>
+  <si>
+    <t>importer168@gmail.com</t>
+  </si>
+  <si>
+    <t>Importer168789</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
-      <name val="Tahoma"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="222"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Tahoma"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="222"/>
-      <family val="2"/>
-      <color theme="10"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <charset val="222"/>
-      <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -63,84 +103,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -440,71 +420,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="16.625" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="13.875" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="29.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Username</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Password</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ระบบ</t>
-        </is>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>woraphitcha.opall@gmail.com</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Opwrpch13</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ผู้กระทำการแทน</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>E-Workpermit</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n"/>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" display="Raweewan68297@mailforeign.com" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/UsernameLogin.xlsx
+++ b/UsernameLogin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\Desktop\E-work\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programing\Thefirst-E-work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB1F36F-8A67-4C8A-90AD-CA9EBBAA1DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F450CE5-1C9D-4F91-96B5-9980438B0F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1110" windowWidth="21390" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Username</t>
   </si>
@@ -46,28 +46,16 @@
   <si>
     <t>ระบบ</t>
   </si>
-  <si>
-    <t>E-Workpermit</t>
-  </si>
-  <si>
-    <t>บริษัทนำเข้า (บนจ.)</t>
-  </si>
-  <si>
-    <t>importer168@gmail.com</t>
-  </si>
-  <si>
-    <t>Importer168789</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -76,7 +64,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -422,15 +410,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="1" max="1" width="29.75" customWidth="1"/>
+    <col min="2" max="2" width="21.375" customWidth="1"/>
+    <col min="3" max="3" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -444,19 +432,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/UsernameLogin.xlsx
+++ b/UsernameLogin.xlsx
@@ -8,32 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programing\Thefirst-E-work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F450CE5-1C9D-4F91-96B5-9980438B0F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A49B52D-8E06-4AA2-BDB0-0188D970602C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3795" yWindow="2670" windowWidth="23760" windowHeight="10200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Username</t>
   </si>
@@ -45,6 +32,18 @@
   </si>
   <si>
     <t>ระบบ</t>
+  </si>
+  <si>
+    <t>info@thefirstgoodman.com</t>
+  </si>
+  <si>
+    <t>Tfg123456</t>
+  </si>
+  <si>
+    <t>บริษัทนำเข้า (บนจ.)</t>
+  </si>
+  <si>
+    <t>E-Workpermit</t>
   </si>
 </sst>
 </file>
@@ -433,9 +432,23 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{B555CAF7-4F8E-4129-85BF-279ADE3565E6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>